--- a/Data/EC/NIT-9005564756.xlsx
+++ b/Data/EC/NIT-9005564756.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\NIYARAKY\MACROS AJUSTADAS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ysarm\OneDrive\Desktop\MACROS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EBAA0331-08A9-4DD5-B344-65DBAFC8A4D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D884AD5-6135-4D31-B7EE-4A2A40638119}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{38FDE33B-EE8D-4D5A-8A1C-7815CFC61178}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{2D55490B-5A77-4384-B9FE-9A204818A2F8}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -71,6 +71,30 @@
     <t>DIANA LUZ MERCADO PRASCA</t>
   </si>
   <si>
+    <t>1905</t>
+  </si>
+  <si>
+    <t>1902</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
     <t>1804</t>
   </si>
   <si>
@@ -86,73 +110,49 @@
     <t>RAYFEB VARGAS MENDOZA</t>
   </si>
   <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>1902</t>
-  </si>
-  <si>
-    <t>1905</t>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>1912</t>
+  </si>
+  <si>
+    <t>1911</t>
+  </si>
+  <si>
+    <t>1910</t>
+  </si>
+  <si>
+    <t>1908</t>
   </si>
   <si>
     <t>1907</t>
-  </si>
-  <si>
-    <t>1908</t>
-  </si>
-  <si>
-    <t>1910</t>
-  </si>
-  <si>
-    <t>1911</t>
-  </si>
-  <si>
-    <t>1912</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>2004</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2010</t>
   </si>
   <si>
     <t>ESTADO DE CUENTA</t>
@@ -251,9 +251,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -266,7 +264,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -466,23 +466,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -510,10 +510,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -551,22 +551,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>667900</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>62300</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>430650</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>121850</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{822234D9-207E-5E7E-F81D-D460C1683617}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15DA1A9C-0329-E0FB-B939-9C0986E26F6A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -588,7 +588,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="921900" y="246450"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -917,23 +917,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{64A82E04-12BA-4F3D-9D1D-9A8E3CE8F3BA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{337EC52D-8FD8-4D43-A854-A3E975C859A3}">
   <dimension ref="B2:J58"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6328125" customWidth="1"/>
-    <col min="2" max="2" width="18.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="32.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="34.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
@@ -946,7 +946,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -957,7 +957,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -968,7 +968,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -979,8 +979,8 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>40</v>
       </c>
@@ -995,8 +995,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1011,8 +1011,8 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>41</v>
       </c>
@@ -1027,8 +1027,8 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>42</v>
       </c>
@@ -1047,7 +1047,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1076,7 +1076,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1090,7 +1090,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="18">
-        <v>29509</v>
+        <v>33125</v>
       </c>
       <c r="G16" s="18">
         <v>828116</v>
@@ -1099,44 +1099,44 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E17" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>11</v>
-      </c>
       <c r="F17" s="18">
-        <v>29509</v>
+        <v>33125</v>
       </c>
       <c r="G17" s="18">
-        <v>737717</v>
+        <v>828116</v>
       </c>
       <c r="H17" s="19"/>
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E18" s="16" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F18" s="18">
-        <v>29509</v>
+        <v>31249</v>
       </c>
       <c r="G18" s="18">
         <v>828116</v>
@@ -1145,7 +1145,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1156,10 +1156,10 @@
         <v>10</v>
       </c>
       <c r="E19" s="16" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F19" s="18">
-        <v>29509</v>
+        <v>31249</v>
       </c>
       <c r="G19" s="18">
         <v>828116</v>
@@ -1168,38 +1168,38 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E20" s="16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F20" s="18">
-        <v>29509</v>
+        <v>31249</v>
       </c>
       <c r="G20" s="18">
-        <v>737717</v>
+        <v>828116</v>
       </c>
       <c r="H20" s="19"/>
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E21" s="16" t="s">
         <v>16</v>
@@ -1214,7 +1214,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1237,41 +1237,41 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D23" s="17" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F23" s="18">
         <v>29509</v>
       </c>
       <c r="G23" s="18">
-        <v>737717</v>
+        <v>828116</v>
       </c>
       <c r="H23" s="19"/>
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D24" s="17" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E24" s="16" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F24" s="18">
         <v>29509</v>
@@ -1283,41 +1283,41 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E25" s="16" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F25" s="18">
         <v>29509</v>
       </c>
       <c r="G25" s="18">
-        <v>828116</v>
+        <v>737717</v>
       </c>
       <c r="H25" s="19"/>
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E26" s="16" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F26" s="18">
         <v>29509</v>
@@ -1329,15 +1329,15 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E27" s="16" t="s">
         <v>18</v>
@@ -1346,50 +1346,50 @@
         <v>29509</v>
       </c>
       <c r="G27" s="18">
-        <v>828116</v>
+        <v>737717</v>
       </c>
       <c r="H27" s="19"/>
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E28" s="16" t="s">
         <v>19</v>
       </c>
       <c r="F28" s="18">
-        <v>31249</v>
+        <v>29509</v>
       </c>
       <c r="G28" s="18">
-        <v>828116</v>
+        <v>737717</v>
       </c>
       <c r="H28" s="19"/>
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F29" s="18">
-        <v>31249</v>
+        <v>27604</v>
       </c>
       <c r="G29" s="18">
         <v>828116</v>
@@ -1398,21 +1398,21 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D30" s="17" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E30" s="16" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F30" s="18">
-        <v>31249</v>
+        <v>33125</v>
       </c>
       <c r="G30" s="18">
         <v>828116</v>
@@ -1421,21 +1421,21 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D31" s="17" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E31" s="16" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F31" s="18">
-        <v>31249</v>
+        <v>33125</v>
       </c>
       <c r="G31" s="18">
         <v>828116</v>
@@ -1444,21 +1444,21 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E32" s="16" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F32" s="18">
-        <v>31249</v>
+        <v>33125</v>
       </c>
       <c r="G32" s="18">
         <v>828116</v>
@@ -1467,21 +1467,21 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C33" s="16" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D33" s="17" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E33" s="16" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F33" s="18">
-        <v>31249</v>
+        <v>33125</v>
       </c>
       <c r="G33" s="18">
         <v>828116</v>
@@ -1490,18 +1490,18 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E34" s="16" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="F34" s="18">
         <v>33125</v>
@@ -1513,21 +1513,21 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D35" s="17" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E35" s="16" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F35" s="18">
-        <v>31249</v>
+        <v>33125</v>
       </c>
       <c r="G35" s="18">
         <v>828116</v>
@@ -1536,18 +1536,18 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="E36" s="16" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F36" s="18">
         <v>33125</v>
@@ -1559,21 +1559,21 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C37" s="16" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D37" s="17" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E37" s="16" t="s">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="F37" s="18">
-        <v>31249</v>
+        <v>33125</v>
       </c>
       <c r="G37" s="18">
         <v>828116</v>
@@ -1582,18 +1582,18 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C38" s="16" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D38" s="17" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E38" s="16" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="F38" s="18">
         <v>33125</v>
@@ -1605,18 +1605,18 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C39" s="16" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D39" s="17" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E39" s="16" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="F39" s="18">
         <v>33125</v>
@@ -1628,18 +1628,18 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="16" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D40" s="17" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E40" s="16" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F40" s="18">
         <v>33125</v>
@@ -1651,18 +1651,18 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="16" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D41" s="17" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E41" s="16" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F41" s="18">
         <v>33125</v>
@@ -1674,18 +1674,18 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="16" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D42" s="17" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E42" s="16" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F42" s="18">
         <v>33125</v>
@@ -1697,18 +1697,18 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="16" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D43" s="17" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E43" s="16" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="F43" s="18">
         <v>33125</v>
@@ -1720,21 +1720,21 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C44" s="16" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D44" s="17" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E44" s="16" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F44" s="18">
-        <v>33125</v>
+        <v>31249</v>
       </c>
       <c r="G44" s="18">
         <v>828116</v>
@@ -1743,21 +1743,21 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C45" s="16" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D45" s="17" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E45" s="16" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="F45" s="18">
-        <v>33125</v>
+        <v>31249</v>
       </c>
       <c r="G45" s="18">
         <v>828116</v>
@@ -1766,21 +1766,21 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="16" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D46" s="17" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="F46" s="18">
-        <v>33125</v>
+        <v>31249</v>
       </c>
       <c r="G46" s="18">
         <v>828116</v>
@@ -1789,21 +1789,21 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C47" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="D47" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E47" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D47" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="E47" s="16" t="s">
-        <v>33</v>
-      </c>
       <c r="F47" s="18">
-        <v>33125</v>
+        <v>31249</v>
       </c>
       <c r="G47" s="18">
         <v>828116</v>
@@ -1812,21 +1812,21 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C48" s="16" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D48" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="E48" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="E48" s="16" t="s">
-        <v>34</v>
-      </c>
       <c r="F48" s="18">
-        <v>33125</v>
+        <v>31249</v>
       </c>
       <c r="G48" s="18">
         <v>828116</v>
@@ -1835,21 +1835,21 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C49" s="16" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D49" s="17" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="F49" s="18">
-        <v>33125</v>
+        <v>29509</v>
       </c>
       <c r="G49" s="18">
         <v>828116</v>
@@ -1858,21 +1858,21 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C50" s="16" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D50" s="17" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="F50" s="18">
-        <v>33125</v>
+        <v>29509</v>
       </c>
       <c r="G50" s="18">
         <v>828116</v>
@@ -1881,21 +1881,21 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C51" s="16" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D51" s="17" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E51" s="16" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="F51" s="18">
-        <v>33125</v>
+        <v>29509</v>
       </c>
       <c r="G51" s="18">
         <v>828116</v>
@@ -1904,21 +1904,21 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="21" t="s">
         <v>8</v>
       </c>
       <c r="C52" s="22" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="D52" s="23" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="E52" s="22" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="F52" s="24">
-        <v>27604</v>
+        <v>29509</v>
       </c>
       <c r="G52" s="24">
         <v>828116</v>
@@ -1927,7 +1927,7 @@
       <c r="I52" s="25"/>
       <c r="J52" s="26"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="32" t="s">
         <v>48</v>
       </c>
@@ -1938,7 +1938,7 @@
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="32" t="s">
         <v>47</v>
       </c>
